--- a/zhul-erp-backend/src/main/resources/document-template/pl-v1.xlsx
+++ b/zhul-erp-backend/src/main/resources/document-template/pl-v1.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +52,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -92,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +117,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,12 +500,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -512,36 +537,43 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>To:</t>
+          <t>To: ${consignee.name}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Date:</t>
+          <t>Date: ${pl.date}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Address:</t>
+          <t>Address: ${consignee.address}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PI No.:</t>
+          <t>PI No.: ${pi.no}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Attn:</t>
+          <t>Attn: ${consignee.contact}  Tel: ${consignee.phone}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CI No.:</t>
+          <t>CI No.: ${ci.no}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Price Term: ${pl.priceTerm}</t>
         </is>
       </c>
     </row>
@@ -583,37 +615,100 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>${item.no}</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>${item.model}</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>${item.qty}</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>${box.netWeight}</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>${box.grossWeight}</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>${box.dimensions}</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>${box.volume}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>${pl.totalBoxes} CTNS</t>
+        </is>
+      </c>
+      <c r="D11" s="4">
+        <f>SUM(D10:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>SUM(E10:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>SUM(F10:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="12">
+        <f>SUM(H10:H10)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>1. COUNTRY OF ORIGIN:</t>
-        </is>
-      </c>
+      <c r="B12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>2. TERMS OF PAYMENT:</t>
-        </is>
-      </c>
+      <c r="B13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>3. PACKAGING:</t>
+          <t>1. COUNTRY OF ORIGIN:</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2. TERMS OF PAYMENT:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3. PACKAGING:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>4. SHIPPING MARK:</t>
         </is>
@@ -623,13 +718,13 @@
   <mergeCells count="13">
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B17:H17"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B12:H12"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
